--- a/artfynd/S 997-2020 artfynd.xlsx
+++ b/artfynd/S 997-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY60"/>
+  <dimension ref="A1:AZ60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506256</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506540</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506541</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506542</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506543</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,6 +1397,11 @@
           <t>Floraväkteri C-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6772426</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1478,6 +1513,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69970811</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1594,6 +1634,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75963939</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1715,6 +1760,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75963940</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1831,6 +1881,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75963941</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1947,6 +2002,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75963942</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2048,6 +2108,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102094774</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2149,6 +2214,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102094777</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2250,6 +2320,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102094778</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2351,6 +2426,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102094781</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2467,6 +2547,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327588</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2588,6 +2673,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75631856</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2704,6 +2794,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69511006</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2820,6 +2915,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69511050</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2936,6 +3036,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69506429</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3052,6 +3157,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69507153</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3168,6 +3278,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510614</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3284,6 +3399,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510809</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3400,6 +3520,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69510810</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3516,6 +3641,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102094791</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3632,6 +3762,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327591</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3748,6 +3883,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327592</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3864,6 +4004,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69529169</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3980,6 +4125,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75905799</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4096,6 +4246,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327596</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4212,6 +4367,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1978979</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4333,6 +4493,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75749712</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4449,6 +4614,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2044023</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4564,6 +4734,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99316927</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4679,6 +4854,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99314462</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4794,6 +4974,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99314461</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4910,6 +5095,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99323472</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5025,6 +5215,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99314796</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5141,6 +5336,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99329105</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5256,6 +5456,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99332705</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5372,6 +5577,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99317279</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5488,6 +5698,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99317281</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5603,6 +5818,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99314466</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5718,6 +5938,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99316923</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5834,6 +6059,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99329104</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5950,6 +6180,11 @@
           <t>Forsmark platsundersökning</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99327109</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6051,6 +6286,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102094783</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6152,6 +6392,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327595</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6253,6 +6498,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327597</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6354,6 +6604,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327598</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6455,6 +6710,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102094782</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6556,6 +6816,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102094779</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6657,6 +6922,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102094785</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6758,6 +7028,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327593</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6859,6 +7134,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102094784</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6960,6 +7240,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103327589</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7076,6 +7361,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6522291</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7192,6 +7482,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56164611</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7308,8 +7603,74 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69562545</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>